--- a/data/trans_orig/P17A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2007</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108055</t>
+          <t>106599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146814</t>
+          <t>146620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190395</t>
+          <t>193109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238328</t>
+          <t>240959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308123</t>
+          <t>310797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371051</t>
+          <t>374763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547198</t>
+          <t>547392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>585957</t>
+          <t>587413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>450023</t>
+          <t>447392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497956</t>
+          <t>495242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1011312</t>
+          <t>1007600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1074240</t>
+          <t>1071566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>166946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216868</t>
+          <t>217565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>278720</t>
+          <t>277031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>335821</t>
+          <t>335453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>462553</t>
+          <t>464538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540477</t>
+          <t>539488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>744932</t>
+          <t>744235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>793600</t>
+          <t>794854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>631572</t>
+          <t>631940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>688673</t>
+          <t>690362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1388716</t>
+          <t>1389705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1466640</t>
+          <t>1464655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123982</t>
+          <t>124945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170034</t>
+          <t>170962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177693</t>
+          <t>177178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>222558</t>
+          <t>223070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312965</t>
+          <t>312038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375492</t>
+          <t>376452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507541</t>
+          <t>506613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>553593</t>
+          <t>552630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461283</t>
+          <t>460771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506148</t>
+          <t>506663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>985924</t>
+          <t>984964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1048451</t>
+          <t>1049378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172823</t>
+          <t>171763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218936</t>
+          <t>219309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295963</t>
+          <t>296290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>357160</t>
+          <t>357617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>486775</t>
+          <t>486163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>561899</t>
+          <t>561621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>721551</t>
+          <t>721178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767664</t>
+          <t>768724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680440</t>
+          <t>679983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741637</t>
+          <t>741310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1416188</t>
+          <t>1416466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1491312</t>
+          <t>1491924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>617762</t>
+          <t>610391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>705959</t>
+          <t>701611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>997604</t>
+          <t>989297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1105986</t>
+          <t>1095103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1636471</t>
+          <t>1642244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1788573</t>
+          <t>1780854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2567915</t>
+          <t>2572263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2656112</t>
+          <t>2663483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2271199</t>
+          <t>2282082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2379581</t>
+          <t>2387888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4862486</t>
+          <t>4870205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5014588</t>
+          <t>5008815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2012</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156659</t>
+          <t>153105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202248</t>
+          <t>202633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213418</t>
+          <t>213006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264837</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>383259</t>
+          <t>382761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452350</t>
+          <t>455600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500236</t>
+          <t>499851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>545825</t>
+          <t>549379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428551</t>
+          <t>429282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>479970</t>
+          <t>480382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>943522</t>
+          <t>940272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1012613</t>
+          <t>1013111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209930</t>
+          <t>210382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266089</t>
+          <t>267027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>318847</t>
+          <t>327401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387857</t>
+          <t>388319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>552047</t>
+          <t>551749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>643401</t>
+          <t>638991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750704</t>
+          <t>749766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>806863</t>
+          <t>806411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>644327</t>
+          <t>643865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>713337</t>
+          <t>704783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1405576</t>
+          <t>1409986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1496930</t>
+          <t>1497228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154616</t>
+          <t>150958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202191</t>
+          <t>202804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204603</t>
+          <t>204574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260002</t>
+          <t>256097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>367412</t>
+          <t>369096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447290</t>
+          <t>442683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>549477</t>
+          <t>548864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>597052</t>
+          <t>600710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516090</t>
+          <t>519995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571489</t>
+          <t>571518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1080470</t>
+          <t>1085077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1160348</t>
+          <t>1158664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161751</t>
+          <t>162866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213159</t>
+          <t>214855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>301366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364330</t>
+          <t>361548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479789</t>
+          <t>475970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>559435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>728760</t>
+          <t>727064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>780168</t>
+          <t>779053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681244</t>
+          <t>684026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742760</t>
+          <t>744208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1430019</t>
+          <t>1428057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1507703</t>
+          <t>1511522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>727602</t>
+          <t>730173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>831428</t>
+          <t>831885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1099220</t>
+          <t>1101719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1215417</t>
+          <t>1213743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1852918</t>
+          <t>1869143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2008479</t>
+          <t>2015001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2581435</t>
+          <t>2580978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2685261</t>
+          <t>2682690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2331821</t>
+          <t>2333495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2448018</t>
+          <t>2445519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4951622</t>
+          <t>4945100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5107183</t>
+          <t>5090958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2016</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169467</t>
+          <t>170678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217599</t>
+          <t>217713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223103</t>
+          <t>222273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273541</t>
+          <t>273711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>408808</t>
+          <t>406502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>477196</t>
+          <t>479473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457201</t>
+          <t>457087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505333</t>
+          <t>504122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399298</t>
+          <t>399128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449736</t>
+          <t>450566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870443</t>
+          <t>868166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>938831</t>
+          <t>941137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239656</t>
+          <t>242143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>297262</t>
+          <t>301121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>324473</t>
+          <t>321139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>388524</t>
+          <t>383973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>578762</t>
+          <t>579495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>667250</t>
+          <t>665601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725169</t>
+          <t>721310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>782775</t>
+          <t>780288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>654389</t>
+          <t>658940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>718440</t>
+          <t>721774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1398094</t>
+          <t>1399743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1486582</t>
+          <t>1485849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153290</t>
+          <t>153561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200193</t>
+          <t>200091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226062</t>
+          <t>225523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>278296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390247</t>
+          <t>386887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461308</t>
+          <t>464124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>559359</t>
+          <t>559461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606262</t>
+          <t>605991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502003</t>
+          <t>506715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>558949</t>
+          <t>559488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1083255</t>
+          <t>1080439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1154316</t>
+          <t>1157676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197170</t>
+          <t>193930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248432</t>
+          <t>246881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278662</t>
+          <t>279358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>342372</t>
+          <t>339312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>493110</t>
+          <t>491779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569619</t>
+          <t>572657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689135</t>
+          <t>690686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>740397</t>
+          <t>743637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701407</t>
+          <t>704467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>765117</t>
+          <t>764421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1411727</t>
+          <t>1408689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1488236</t>
+          <t>1489567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>798675</t>
+          <t>799914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>905200</t>
+          <t>906779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1104722</t>
+          <t>1110662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1218369</t>
+          <t>1227594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1942331</t>
+          <t>1941723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2101129</t>
+          <t>2090482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2489150</t>
+          <t>2487571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2595675</t>
+          <t>2594436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2326173</t>
+          <t>2316948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2439820</t>
+          <t>2433880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4837763</t>
+          <t>4848410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4996561</t>
+          <t>4997169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2023</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95361</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133616</t>
+          <t>131782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>151805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186500</t>
+          <t>189566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253347</t>
+          <t>256031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305533</t>
+          <t>309128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>503659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>540080</t>
+          <t>539671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>488129</t>
+          <t>485063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523822</t>
+          <t>522824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1004537</t>
+          <t>1000942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1056723</t>
+          <t>1054039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95479</t>
+          <t>88089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241600</t>
+          <t>241543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195606</t>
+          <t>193975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>238992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>263311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>464324</t>
+          <t>470108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>951321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1097385</t>
+          <t>1104775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>716188</t>
+          <t>718223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761609</t>
+          <t>763240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1685755</t>
+          <t>1679971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1883946</t>
+          <t>1886768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111794</t>
+          <t>112014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157201</t>
+          <t>158862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79340</t>
+          <t>74592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203040</t>
+          <t>201413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178986</t>
+          <t>188017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334326</t>
+          <t>334119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546663</t>
+          <t>545002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>592070</t>
+          <t>591850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>730326</t>
+          <t>731953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>854026</t>
+          <t>858774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1302903</t>
+          <t>1303110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1458243</t>
+          <t>1449212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183894</t>
+          <t>184085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240141</t>
+          <t>241048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304991</t>
+          <t>305556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>520713</t>
+          <t>526213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>508346</t>
+          <t>508477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>756195</t>
+          <t>757823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>686069</t>
+          <t>685162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>742316</t>
+          <t>742125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>572710</t>
+          <t>567210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788432</t>
+          <t>787867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1263438</t>
+          <t>1261810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1511287</t>
+          <t>1511156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>487465</t>
+          <t>483831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>704610</t>
+          <t>712631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>765541</t>
+          <t>758693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1041671</t>
+          <t>1050300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1356635</t>
+          <t>1355095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1718072</t>
+          <t>1718603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2753769</t>
+          <t>2745748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2970914</t>
+          <t>2974548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2616962</t>
+          <t>2608333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2893092</t>
+          <t>2899940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5398940</t>
+          <t>5398409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5760377</t>
+          <t>5761917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106599</t>
+          <t>105934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146620</t>
+          <t>147811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>193109</t>
+          <t>190767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240959</t>
+          <t>238268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310797</t>
+          <t>311942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374763</t>
+          <t>373481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547392</t>
+          <t>546201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>587413</t>
+          <t>588078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447392</t>
+          <t>450083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>495242</t>
+          <t>497584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1007600</t>
+          <t>1008882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1071566</t>
+          <t>1070421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166946</t>
+          <t>167540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217565</t>
+          <t>219975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277031</t>
+          <t>279100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>335453</t>
+          <t>337567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>464538</t>
+          <t>462804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>539488</t>
+          <t>541890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>744235</t>
+          <t>741825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>794854</t>
+          <t>794260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>631940</t>
+          <t>629826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>690362</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1389705</t>
+          <t>1387303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1464655</t>
+          <t>1466389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124945</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170962</t>
+          <t>168215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177178</t>
+          <t>177091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223070</t>
+          <t>222450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312038</t>
+          <t>312928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>376452</t>
+          <t>376967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506613</t>
+          <t>509360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>552630</t>
+          <t>554626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460771</t>
+          <t>461391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506663</t>
+          <t>506750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>984964</t>
+          <t>984449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1049378</t>
+          <t>1048488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171763</t>
+          <t>173560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219309</t>
+          <t>222854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>296290</t>
+          <t>297210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>357617</t>
+          <t>357369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>34,44%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>523023</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>485564</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>564943</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>24,55%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>28,56%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>523023</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>486163</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>561621</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>721178</t>
+          <t>717633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>768724</t>
+          <t>766927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679983</t>
+          <t>680231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741310</t>
+          <t>740390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>71,36%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1455064</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1413144</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1492523</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>73,56%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>71,44%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1455064</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1416466</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1491924</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>73,56%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>71,61%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>610391</t>
+          <t>615137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>701611</t>
+          <t>706471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>989297</t>
+          <t>994968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1095103</t>
+          <t>1102982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1642244</t>
+          <t>1635480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1780854</t>
+          <t>1776710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2572263</t>
+          <t>2567403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2663483</t>
+          <t>2658737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2282082</t>
+          <t>2274203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2387888</t>
+          <t>2382217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4870205</t>
+          <t>4874349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5008815</t>
+          <t>5015579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153105</t>
+          <t>156769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202633</t>
+          <t>204993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213006</t>
+          <t>210958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264106</t>
+          <t>261445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382761</t>
+          <t>385226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455600</t>
+          <t>454271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499851</t>
+          <t>497491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>549379</t>
+          <t>545715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429282</t>
+          <t>431943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>480382</t>
+          <t>482430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940272</t>
+          <t>941601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1013111</t>
+          <t>1010646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>210382</t>
+          <t>211300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267027</t>
+          <t>265311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327401</t>
+          <t>323290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>388319</t>
+          <t>385179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551749</t>
+          <t>551571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638991</t>
+          <t>638177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>749766</t>
+          <t>751482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>806411</t>
+          <t>805493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>643865</t>
+          <t>647005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>704783</t>
+          <t>708894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1409986</t>
+          <t>1410800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1497228</t>
+          <t>1497406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150958</t>
+          <t>151927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202804</t>
+          <t>201978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>206061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256097</t>
+          <t>258631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369096</t>
+          <t>373441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>442683</t>
+          <t>448821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>548864</t>
+          <t>549690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600710</t>
+          <t>599741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519995</t>
+          <t>517461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571518</t>
+          <t>570031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1085077</t>
+          <t>1078939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1158664</t>
+          <t>1154319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162866</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214855</t>
+          <t>215371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301366</t>
+          <t>301299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361548</t>
+          <t>361971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>475970</t>
+          <t>476797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>559435</t>
+          <t>557369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>727064</t>
+          <t>726548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>779053</t>
+          <t>777887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>684026</t>
+          <t>683603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744208</t>
+          <t>744275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1428057</t>
+          <t>1430123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1511522</t>
+          <t>1510695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>730173</t>
+          <t>728996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>831885</t>
+          <t>833045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1101719</t>
+          <t>1099160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1213743</t>
+          <t>1211669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1869143</t>
+          <t>1859772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2015001</t>
+          <t>2011120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2580978</t>
+          <t>2579818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2682690</t>
+          <t>2683867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2333495</t>
+          <t>2335569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2445519</t>
+          <t>2448078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4945100</t>
+          <t>4948981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5090958</t>
+          <t>5100329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170678</t>
+          <t>169643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217713</t>
+          <t>217856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222273</t>
+          <t>223297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273711</t>
+          <t>274071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>406502</t>
+          <t>409138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>479473</t>
+          <t>478645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457087</t>
+          <t>456944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504122</t>
+          <t>505157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399128</t>
+          <t>398768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>450566</t>
+          <t>449542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>868166</t>
+          <t>868994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941137</t>
+          <t>938501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242143</t>
+          <t>237001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301121</t>
+          <t>298033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>321139</t>
+          <t>322567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>383973</t>
+          <t>385828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>579495</t>
+          <t>581766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>665601</t>
+          <t>670195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721310</t>
+          <t>724398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>780288</t>
+          <t>785430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>658940</t>
+          <t>657085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>721774</t>
+          <t>720346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1399743</t>
+          <t>1395149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1485849</t>
+          <t>1483578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153561</t>
+          <t>153313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200091</t>
+          <t>199937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225523</t>
+          <t>225657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>278296</t>
+          <t>279404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>386887</t>
+          <t>387410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>464124</t>
+          <t>460573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>559461</t>
+          <t>559615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605991</t>
+          <t>606239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506715</t>
+          <t>505607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>559488</t>
+          <t>559354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1080439</t>
+          <t>1083990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1157676</t>
+          <t>1157153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193930</t>
+          <t>196138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246881</t>
+          <t>245906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>279358</t>
+          <t>275113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>339312</t>
+          <t>341546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491779</t>
+          <t>490491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>572657</t>
+          <t>569662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>690686</t>
+          <t>691661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>743637</t>
+          <t>741429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704467</t>
+          <t>702233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>764421</t>
+          <t>768666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408689</t>
+          <t>1411684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1489567</t>
+          <t>1490855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>799914</t>
+          <t>810478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>906779</t>
+          <t>907318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1110662</t>
+          <t>1112386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1227594</t>
+          <t>1217719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1941723</t>
+          <t>1944005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2090482</t>
+          <t>2099412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2487571</t>
+          <t>2487032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2594436</t>
+          <t>2583872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2316948</t>
+          <t>2326823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2433880</t>
+          <t>2432156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4848410</t>
+          <t>4839480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4997169</t>
+          <t>4994887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>102778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131782</t>
+          <t>142870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151805</t>
+          <t>159763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189566</t>
+          <t>198423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256031</t>
+          <t>274499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309128</t>
+          <t>331366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>522333</t>
+          <t>569950</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503659</t>
+          <t>547840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>539671</t>
+          <t>587932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>506546</t>
+          <t>552227</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>485063</t>
+          <t>533620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>522824</t>
+          <t>572280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1028879</t>
+          <t>1122177</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1000942</t>
+          <t>1091386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1054039</t>
+          <t>1148253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674629</t>
+          <t>732043</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674629</t>
+          <t>732043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674629</t>
+          <t>732043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310070</t>
+          <t>1422752</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310070</t>
+          <t>1422752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310070</t>
+          <t>1422752</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>184235</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88089</t>
+          <t>177298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241543</t>
+          <t>232376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193975</t>
+          <t>221504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238992</t>
+          <t>269596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>401280</t>
+          <t>449820</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263311</t>
+          <t>414441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470108</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1008629</t>
+          <t>844624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951321</t>
+          <t>816541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1104775</t>
+          <t>871619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>740170</t>
+          <t>824379</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718223</t>
+          <t>800310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>763240</t>
+          <t>848402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1748799</t>
+          <t>1669003</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1679971</t>
+          <t>1627895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1886768</t>
+          <t>1704382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957215</t>
+          <t>1069906</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957215</t>
+          <t>1069906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957215</t>
+          <t>1069906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150079</t>
+          <t>2118823</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150079</t>
+          <t>2118823</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150079</t>
+          <t>2118823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>124187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158862</t>
+          <t>172116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>160020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201413</t>
+          <t>202249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188017</t>
+          <t>295694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334119</t>
+          <t>360473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>570199</t>
+          <t>655834</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545002</t>
+          <t>630051</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591850</t>
+          <t>677980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>784584</t>
+          <t>632505</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>731953</t>
+          <t>610010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>858774</t>
+          <t>652239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1354782</t>
+          <t>1288340</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303110</t>
+          <t>1253953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1449212</t>
+          <t>1318732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703864</t>
+          <t>802167</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703864</t>
+          <t>802167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703864</t>
+          <t>802167</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637229</t>
+          <t>1614426</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637229</t>
+          <t>1614426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637229</t>
+          <t>1614426</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>210347</t>
+          <t>219239</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184085</t>
+          <t>193266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241048</t>
+          <t>248096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>362652</t>
+          <t>321523</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305556</t>
+          <t>294793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>526213</t>
+          <t>351145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>540763</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>508477</t>
+          <t>503895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>757823</t>
+          <t>580961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>715863</t>
+          <t>770155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>685162</t>
+          <t>741298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>742125</t>
+          <t>796128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>730771</t>
+          <t>794896</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>567210</t>
+          <t>765274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>821626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1446634</t>
+          <t>1565051</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1261810</t>
+          <t>1524853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1511156</t>
+          <t>1601919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926210</t>
+          <t>989394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926210</t>
+          <t>989394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926210</t>
+          <t>989394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093423</t>
+          <t>1116419</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093423</t>
+          <t>1116419</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093423</t>
+          <t>1116419</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019633</t>
+          <t>2105814</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019633</t>
+          <t>2105814</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019633</t>
+          <t>2105814</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483831</t>
+          <t>642263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>712631</t>
+          <t>746952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>758693</t>
+          <t>881086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1050300</t>
+          <t>972095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1355095</t>
+          <t>1547884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1718603</t>
+          <t>1683892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2817024</t>
+          <t>2840564</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2745748</t>
+          <t>2784236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2974548</t>
+          <t>2888925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2762071</t>
+          <t>2804006</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2608333</t>
+          <t>2758531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2899940</t>
+          <t>2849540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5579095</t>
+          <t>5644570</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5398409</t>
+          <t>5577922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5761917</t>
+          <t>5713930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
